--- a/outputs/daily/hr_rankings_2026-08-14.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-14.xlsx
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6303,32 +6303,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-14T23:10:00Z</t>
+          <t>2026-08-14T23:15:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -6366,17 +6366,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>50.8</v>
+        <v>43.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>54.7</v>
+        <v>63.1</v>
       </c>
       <c r="R22" t="n">
-        <v>41.1</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="S22" t="n">
         <v>86.40000000000001</v>
@@ -6385,7 +6385,7 @@
         <v>80</v>
       </c>
       <c r="U22" t="n">
-        <v>90.59999999999999</v>
+        <v>28.9</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6437,27 +6437,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.2% barrel, 8.7 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -6467,12 +6467,12 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>42.53</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
@@ -6482,97 +6482,97 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>100.7616</t>
+          <t>100.5405</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>0.397</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.2144</t>
+          <t>0.1819</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>26.84</t>
+          <t>34.42</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>53.17</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.1804</t>
+          <t>0.1942</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>45.47</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.4022</t>
+          <t>0.5224</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.2327</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>24.63</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6583,32 +6583,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jazz Chisholm Jr.</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-14T23:15:00Z</t>
+          <t>2026-08-14T23:10:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>59.9</v>
+        <v>59.7</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6646,17 +6646,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>43.2</v>
+        <v>50.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>63.1</v>
+        <v>54.7</v>
       </c>
       <c r="R23" t="n">
-        <v>64.90000000000001</v>
+        <v>40.1</v>
       </c>
       <c r="S23" t="n">
         <v>86.40000000000001</v>
@@ -6665,7 +6665,7 @@
         <v>80</v>
       </c>
       <c r="U23" t="n">
-        <v>28.9</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -6717,27 +6717,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.2% barrel, 8.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
@@ -6762,97 +6762,97 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>100.5405</t>
+          <t>100.7616</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>0.476</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.1819</t>
+          <t>0.2144</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.3379</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>34.42</t>
+          <t>26.84</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>53.17</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.36</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.1942</t>
+          <t>0.1804</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>45.47</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.5224</t>
+          <t>0.4022</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.2327</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>24.63</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -7143,47 +7143,47 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-14T23:10:00Z</t>
+          <t>2026-08-14T23:15:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7206,26 +7206,26 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>53.4</v>
+        <v>47.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>54.7</v>
+        <v>41.7</v>
       </c>
       <c r="R25" t="n">
-        <v>41.1</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U25" t="n">
-        <v>80.8</v>
+        <v>26.4</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -7277,142 +7277,142 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>92.67</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>104.275</t>
+          <t>103.4256</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.4684</t>
+          <t>0.4716</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.1855</t>
+          <t>0.1872</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.3644</t>
+          <t>0.3381</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>75.51</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>22.56</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.1507</t>
+          <t>0.1873</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>89.26</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>0.4022</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr"/>
@@ -7423,47 +7423,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-14T23:15:00Z</t>
+          <t>2026-08-14T23:10:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7486,26 +7486,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>47.5</v>
+        <v>53.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>41.7</v>
+        <v>54.7</v>
       </c>
       <c r="R26" t="n">
-        <v>72.40000000000001</v>
+        <v>40.1</v>
       </c>
       <c r="S26" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T26" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U26" t="n">
-        <v>26.4</v>
+        <v>80.8</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -7557,142 +7557,142 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 13.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>92.67</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>103.4256</t>
+          <t>104.275</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.4716</t>
+          <t>0.4684</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.1872</t>
+          <t>0.1855</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.3381</t>
+          <t>0.3644</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>75.51</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>57.91</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>34.52</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>22.56</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1873</t>
+          <t>0.1507</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.4022</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11332,7 +11332,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -11867,22 +11867,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -11892,22 +11892,22 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Chris Bassitt</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>605135</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -11934,22 +11934,22 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>50.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>54.7</v>
+        <v>25.8</v>
       </c>
       <c r="R42" t="n">
         <v>41.1</v>
       </c>
       <c r="S42" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T42" t="n">
         <v>50</v>
       </c>
       <c r="U42" t="n">
-        <v>15.3</v>
+        <v>65.8</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -12001,142 +12001,142 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.4% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>13.86</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>47.02</t>
+          <t>50.91</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>92.82</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>102.0721</t>
+          <t>105.3161</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>0.4509</t>
+          <t>0.5108</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.1988</t>
+          <t>0.2418</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>0.3375</t>
+          <t>0.3656</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>74.71</t>
+          <t>79.41</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>85.32</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.1962</t>
+          <t>0.2731</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>0.4022</t>
+          <t>0.4049</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1308</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr"/>
@@ -12147,22 +12147,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Chris Bassitt</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>605135</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -12196,7 +12196,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>54.8</v>
+        <v>54.6</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -12210,26 +12210,26 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>64.59999999999999</v>
+        <v>32.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>25.8</v>
+        <v>56.6</v>
       </c>
       <c r="R43" t="n">
-        <v>41.1</v>
+        <v>47.8</v>
       </c>
       <c r="S43" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T43" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U43" t="n">
-        <v>65.8</v>
+        <v>52.3</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
@@ -12291,132 +12291,132 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.4% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>13.86</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>50.91</t>
+          <t>38.07</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>88.62</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>105.3161</t>
+          <t>98.7688</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>0.5108</t>
+          <t>0.4259</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.2418</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.3656</t>
+          <t>0.3235</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>85.32</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>32.97</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.2731</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>35.72</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>0.4049</t>
+          <t>0.5415</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>0.1308</t>
+          <t>0.246</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>32.72</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr"/>
@@ -12427,22 +12427,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12457,17 +12457,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -12490,26 +12490,26 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>32.4</v>
+        <v>50.6</v>
       </c>
       <c r="Q44" t="n">
-        <v>56.6</v>
+        <v>54.7</v>
       </c>
       <c r="R44" t="n">
-        <v>47.8</v>
+        <v>40.1</v>
       </c>
       <c r="S44" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T44" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U44" t="n">
-        <v>52.3</v>
+        <v>15.3</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -12561,142 +12561,142 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>47.02</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>88.62</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>98.7688</t>
+          <t>102.0721</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.4259</t>
+          <t>0.4509</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.1988</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.3235</t>
+          <t>0.3375</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>74.71</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1962</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>0.5415</t>
+          <t>0.4022</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>32.72</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr"/>
@@ -12732,7 +12732,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -12756,7 +12756,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>54.6</v>
+        <v>54.4</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>54.7</v>
       </c>
       <c r="R45" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S45" t="n">
         <v>94.90000000000001</v>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -14416,7 +14416,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -17184,7 +17184,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -17439,22 +17439,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>677588</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>José Tena</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -17464,22 +17464,22 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>650633</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -17488,7 +17488,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -17502,26 +17502,26 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>35.9</v>
+        <v>34.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>41</v>
+        <v>56.6</v>
       </c>
       <c r="R62" t="n">
-        <v>41.1</v>
+        <v>47.8</v>
       </c>
       <c r="S62" t="n">
-        <v>100</v>
+        <v>76.2</v>
       </c>
       <c r="T62" t="n">
         <v>80</v>
       </c>
       <c r="U62" t="n">
-        <v>58.4</v>
+        <v>37.8</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -17556,7 +17556,7 @@
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr"/>
@@ -17573,14 +17573,14 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="AJ62" t="inlineStr">
         <is>
           <t>1</t>
@@ -17588,117 +17588,117 @@
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Contact streak: 12/31 over last 7 games</t>
+          <t>Last 7 games: 3/12, 1 HR</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.66</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>101.5184</t>
+          <t>101.9048</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>0.3738</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.1336</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>0.3048</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.94</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.1421</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>35.72</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>0.4102</t>
+          <t>0.5415</t>
         </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.246</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>32.72</t>
         </is>
       </c>
       <c r="BG62" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH62" t="inlineStr">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr"/>
@@ -17719,12 +17719,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>694197</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Angel Genao</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -17744,12 +17744,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -17768,7 +17768,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17782,26 +17782,26 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>52.8</v>
+        <v>35.9</v>
       </c>
       <c r="Q63" t="n">
-        <v>39.4</v>
+        <v>41</v>
       </c>
       <c r="R63" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S63" t="n">
-        <v>76.2</v>
+        <v>100</v>
       </c>
       <c r="T63" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U63" t="n">
-        <v>27.6</v>
+        <v>58.4</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -17853,12 +17853,12 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -17868,82 +17868,82 @@
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Contact streak: 12/31 over last 7 games</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>100.8749</t>
+          <t>101.5184</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.435</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.349</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
@@ -17983,7 +17983,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI63" t="inlineStr">
@@ -17999,22 +17999,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>677588</t>
+          <t>694197</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>José Tena</t>
+          <t>Angel Genao</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -18034,12 +18034,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>650633</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -18048,7 +18048,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -18062,26 +18062,26 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>34.2</v>
+        <v>52.8</v>
       </c>
       <c r="Q64" t="n">
-        <v>56.6</v>
+        <v>39.4</v>
       </c>
       <c r="R64" t="n">
-        <v>47.8</v>
+        <v>40.1</v>
       </c>
       <c r="S64" t="n">
         <v>76.2</v>
       </c>
       <c r="T64" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U64" t="n">
-        <v>37.8</v>
+        <v>27.6</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr"/>
@@ -18133,12 +18133,12 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -18148,127 +18148,127 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/12, 1 HR</t>
+          <t>Last 7 games: 4/22, 1 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>101.9048</t>
+          <t>100.8749</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>0.3738</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>0.1336</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.3048</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>72.94</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.1421</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>0.5415</t>
+          <t>0.4102</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>32.72</t>
+          <t>27.61</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -18864,7 +18864,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -19672,7 +19672,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -20512,7 +20512,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -20536,7 +20536,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>41</v>
       </c>
       <c r="R73" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S73" t="n">
         <v>94.90000000000001</v>
@@ -20751,7 +20751,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI73" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -22192,7 +22192,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -24659,22 +24659,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>657757</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Gavin Sheets</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -24684,22 +24684,22 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Chris Bassitt</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>605135</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24722,26 +24722,26 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>34.7</v>
+        <v>45.2</v>
       </c>
       <c r="Q88" t="n">
-        <v>54.7</v>
+        <v>25.8</v>
       </c>
       <c r="R88" t="n">
         <v>41.1</v>
       </c>
       <c r="S88" t="n">
-        <v>64.3</v>
+        <v>76.2</v>
       </c>
       <c r="T88" t="n">
         <v>80</v>
       </c>
       <c r="U88" t="n">
-        <v>20.3</v>
+        <v>57.6</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -24793,27 +24793,27 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.4% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
@@ -24823,112 +24823,112 @@
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>88.22</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>99.6783</t>
+          <t>100.2175</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.4054</t>
+          <t>0.4269</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.1655</t>
+          <t>0.1963</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>0.3221</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>74.52</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>48.16</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>23.21</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.1798</t>
+          <t>0.2141</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.4022</t>
+          <t>0.4049</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1308</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -24939,22 +24939,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>657757</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Victor Mesa Jr.</t>
+          <t>Gavin Sheets</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -24964,22 +24964,22 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Chris Bassitt</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>605135</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -24988,7 +24988,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -25002,26 +25002,26 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>45.2</v>
+        <v>34.7</v>
       </c>
       <c r="Q89" t="n">
-        <v>25.8</v>
+        <v>54.7</v>
       </c>
       <c r="R89" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S89" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="T89" t="n">
         <v>80</v>
       </c>
       <c r="U89" t="n">
-        <v>57.6</v>
+        <v>20.3</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -25073,27 +25073,27 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/15, 1 HR</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.4% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
@@ -25103,112 +25103,112 @@
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>88.22</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>100.2175</t>
+          <t>99.6783</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>0.4269</t>
+          <t>0.4054</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>0.1963</t>
+          <t>0.1655</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>0.3221</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>74.52</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>48.16</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>23.21</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>0.2141</t>
+          <t>0.1798</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD89" t="inlineStr">
         <is>
-          <t>0.4049</t>
+          <t>0.4022</t>
         </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
-          <t>0.1308</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="BG89" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI89" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ89" t="inlineStr"/>
@@ -25524,7 +25524,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -25804,7 +25804,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -25828,7 +25828,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>39.4</v>
       </c>
       <c r="R92" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S92" t="n">
         <v>96.59999999999999</v>
@@ -26043,7 +26043,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI92" t="inlineStr">
@@ -26364,7 +26364,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -26644,7 +26644,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -27764,7 +27764,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -28044,7 +28044,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>54.7</v>
       </c>
       <c r="R100" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S100" t="n">
         <v>100</v>
@@ -28283,7 +28283,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI100" t="inlineStr">
@@ -28324,7 +28324,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -29164,7 +29164,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -32195,27 +32195,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>669134</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-14T23:10:00Z</t>
+          <t>2026-08-15T02:15:00Z</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -32225,17 +32225,17 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Landen Roupp</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>694738</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -32258,26 +32258,26 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>23.1</v>
+        <v>31.5</v>
       </c>
       <c r="Q115" t="n">
-        <v>54.7</v>
+        <v>18.4</v>
       </c>
       <c r="R115" t="n">
-        <v>41.1</v>
+        <v>50.3</v>
       </c>
       <c r="S115" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T115" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U115" t="n">
-        <v>52.5</v>
+        <v>40.7</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -32329,12 +32329,12 @@
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -32344,12 +32344,12 @@
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL115" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.6% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
@@ -32359,112 +32359,112 @@
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>88.29</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>99.058</t>
+          <t>100.0177</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.3883</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>0.1127</t>
+          <t>0.1554</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>0.3088</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>26.18</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>42.46</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>0.1386</t>
+          <t>0.1547</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>86.79</t>
         </is>
       </c>
       <c r="BD115" t="inlineStr">
         <is>
-          <t>0.4022</t>
+          <t>0.3513</t>
         </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1183</t>
         </is>
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BG115" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI115" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ115" t="inlineStr"/>
@@ -32475,47 +32475,47 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>669134</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-15T02:15:00Z</t>
+          <t>2026-08-14T23:10:00Z</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Landen Roupp</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>694738</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -32524,7 +32524,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -32538,26 +32538,26 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>31.5</v>
+        <v>23.1</v>
       </c>
       <c r="Q116" t="n">
-        <v>18.4</v>
+        <v>54.7</v>
       </c>
       <c r="R116" t="n">
-        <v>50.3</v>
+        <v>40.1</v>
       </c>
       <c r="S116" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T116" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U116" t="n">
-        <v>40.7</v>
+        <v>52.5</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -32609,12 +32609,12 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -32624,12 +32624,12 @@
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.6% barrel, 9.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
@@ -32639,112 +32639,112 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>7.97</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>88.29</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>100.0177</t>
+          <t>99.058</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>0.3883</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>0.1554</t>
+          <t>0.1127</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>0.3088</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>72.51</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>26.18</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>42.46</t>
+          <t>48.03</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>0.1547</t>
+          <t>0.1386</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>86.79</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>0.3513</t>
+          <t>0.4022</t>
         </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
-          <t>0.1183</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI116" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ116" t="inlineStr"/>
@@ -32780,7 +32780,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -33336,7 +33336,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -36639,56 +36639,56 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>682988</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Tyler Locklear</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-14T23:10:00Z</t>
+          <t>2026-08-14T23:15:00Z</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>650633</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -36702,50 +36702,42 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P131" t="n">
-        <v>21.6</v>
+        <v>32.2</v>
       </c>
       <c r="Q131" t="n">
-        <v>41</v>
+        <v>21.9</v>
       </c>
       <c r="R131" t="n">
-        <v>41.1</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="S131" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T131" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U131" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="W131" t="inlineStr"/>
+      <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -36753,10 +36745,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr"/>
@@ -36778,7 +36774,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
@@ -36788,12 +36784,12 @@
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Contact streak: 4/12 over last 7 games</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 8.9 HR allowed</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
@@ -36803,112 +36799,112 @@
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>35.82</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>98.6053</t>
+          <t>98.3699</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>0.4025</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1647</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.89</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>87.41</t>
         </is>
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>0.4102</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1101</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH131" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BI131" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ131" t="inlineStr"/>
@@ -36919,22 +36915,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>682988</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tyler Locklear</t>
+          <t>Andrés Giménez</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -36944,27 +36940,27 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Gerrit Cole</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>543037</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -36982,57 +36978,61 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P132" t="n">
-        <v>32.2</v>
+        <v>7.2</v>
       </c>
       <c r="Q132" t="n">
-        <v>21.9</v>
+        <v>44.2</v>
       </c>
       <c r="R132" t="n">
-        <v>72.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="S132" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T132" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U132" t="n">
-        <v>32</v>
+        <v>42.3</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr"/>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y132" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr"/>
@@ -37049,142 +37049,142 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Contact streak: 4/12 over last 7 games</t>
+          <t>Last 7 games: 7/25, 1 HR</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 8.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>35.82</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>98.3699</t>
+          <t>95.8863</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
         <is>
-          <t>0.4025</t>
+          <t>0.3351</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>0.1647</t>
+          <t>0.0971</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2814</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>71.89</t>
+          <t>68.46</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.1156</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>87.41</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="BD132" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
-          <t>0.1101</t>
+          <t>0.138</t>
         </is>
       </c>
       <c r="BF132" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="BG132" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH132" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI132" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ132" t="inlineStr"/>
@@ -37195,47 +37195,47 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Andrés Giménez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-14T23:15:00Z</t>
+          <t>2026-08-14T23:10:00Z</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Gerrit Cole</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>543037</t>
+          <t>650633</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -37244,7 +37244,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -37262,22 +37262,22 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>7.2</v>
+        <v>21.6</v>
       </c>
       <c r="Q133" t="n">
-        <v>44.2</v>
+        <v>41</v>
       </c>
       <c r="R133" t="n">
-        <v>64.90000000000001</v>
+        <v>40.1</v>
       </c>
       <c r="S133" t="n">
-        <v>76.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T133" t="n">
         <v>80</v>
       </c>
       <c r="U133" t="n">
-        <v>42.3</v>
+        <v>7</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
@@ -37312,7 +37312,7 @@
       <c r="AB133" t="inlineStr"/>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr"/>
@@ -37329,142 +37329,142 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 1 HR</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>95.8863</t>
+          <t>98.6053</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
         <is>
-          <t>0.3351</t>
+          <t>0.349</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>0.0971</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr">
         <is>
-          <t>0.2814</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>68.46</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>0.1156</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="BD133" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.4102</t>
         </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF133" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>27.61</t>
         </is>
       </c>
       <c r="BG133" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH133" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI133" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ133" t="inlineStr"/>
@@ -37780,7 +37780,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -38060,7 +38060,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -38340,7 +38340,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -39155,52 +39155,52 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>593428</t>
+          <t>672695</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Geraldo Perdomo</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-14T23:10:00Z</t>
+          <t>2026-08-14T23:15:00Z</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -39218,50 +39218,42 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P140" t="n">
-        <v>27.2</v>
+        <v>14.2</v>
       </c>
       <c r="Q140" t="n">
-        <v>54.7</v>
+        <v>21</v>
       </c>
       <c r="R140" t="n">
-        <v>41.1</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="S140" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T140" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U140" t="n">
-        <v>25.3</v>
+        <v>19.5</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="W140" t="inlineStr"/>
+      <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -39269,7 +39261,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr"/>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC140" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39289,27 +39285,27 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL140" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.0% barrel, 8.9 HR allowed</t>
         </is>
       </c>
       <c r="AM140" t="inlineStr">
@@ -39319,47 +39315,47 @@
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>39.62</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>87.32</t>
         </is>
       </c>
       <c r="AQ140" t="inlineStr">
         <is>
-          <t>99.866</t>
+          <t>96.6324</t>
         </is>
       </c>
       <c r="AR140" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1082</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr">
         <is>
-          <t>0.3221</t>
+          <t>0.3364</t>
         </is>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>72.38</t>
+          <t>67.36</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
@@ -39369,62 +39365,62 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>0.1105</t>
+          <t>0.1419</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>87.41</t>
         </is>
       </c>
       <c r="BD140" t="inlineStr">
         <is>
-          <t>0.4022</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="BE140" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1101</t>
         </is>
       </c>
       <c r="BF140" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="BG140" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH140" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BI140" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ140" t="inlineStr"/>
@@ -39435,24 +39431,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>672695</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Geraldo Perdomo</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F141" t="inlineStr">
         <is>
           <t>2026-08-14T23:15:00Z</t>
@@ -39460,31 +39456,31 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
@@ -39498,54 +39494,58 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P141" t="n">
-        <v>14.2</v>
+        <v>11.1</v>
       </c>
       <c r="Q141" t="n">
-        <v>21</v>
+        <v>41.7</v>
       </c>
       <c r="R141" t="n">
         <v>72.40000000000001</v>
       </c>
       <c r="S141" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T141" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U141" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="V141" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y141" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB141" t="inlineStr"/>
       <c r="AC141" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39565,12 +39565,12 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
@@ -39580,12 +39580,12 @@
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 0 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL141" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.0% barrel, 8.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
@@ -39595,97 +39595,97 @@
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>87.32</t>
+          <t>86.18</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>96.6324</t>
+          <t>96.3994</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.366</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>0.1082</t>
+          <t>0.1043</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr">
         <is>
-          <t>0.3364</t>
+          <t>0.2983</t>
         </is>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>67.36</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>32.45</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>25.16</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>0.1419</t>
+          <t>0.1266</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>87.41</t>
+          <t>89.26</t>
         </is>
       </c>
       <c r="BD141" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
-          <t>0.1101</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="BG141" t="inlineStr">
@@ -39711,27 +39711,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>664983</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mauricio Dubón</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-14T23:15:00Z</t>
+          <t>2026-08-15T02:15:00Z</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -39741,17 +39741,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Landen Roupp</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>694738</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -39774,26 +39774,26 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="Q142" t="n">
-        <v>41.7</v>
+        <v>19.5</v>
       </c>
       <c r="R142" t="n">
-        <v>72.40000000000001</v>
+        <v>50.3</v>
       </c>
       <c r="S142" t="n">
-        <v>76.2</v>
+        <v>93.2</v>
       </c>
       <c r="T142" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U142" t="n">
-        <v>32</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
@@ -39807,7 +39807,7 @@
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -39845,27 +39845,27 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
@@ -39875,112 +39875,112 @@
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>86.18</t>
+          <t>84.98</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>96.3994</t>
+          <t>96.7242</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.3999</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>0.1043</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>0.2983</t>
+          <t>0.3091</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>70.75</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>37.66</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>25.16</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>0.1266</t>
+          <t>0.1858</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>86.79</t>
         </is>
       </c>
       <c r="BD142" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3513</t>
         </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1183</t>
         </is>
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BG142" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH142" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI142" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ142" t="inlineStr"/>
@@ -39991,47 +39991,47 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>664983</t>
+          <t>593428</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-08-15T02:15:00Z</t>
+          <t>2026-08-14T23:10:00Z</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Landen Roupp</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>694738</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -40040,7 +40040,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -40054,26 +40054,26 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P143" t="n">
-        <v>15.3</v>
+        <v>27.2</v>
       </c>
       <c r="Q143" t="n">
-        <v>19.5</v>
+        <v>54.7</v>
       </c>
       <c r="R143" t="n">
-        <v>50.3</v>
+        <v>40.1</v>
       </c>
       <c r="S143" t="n">
-        <v>93.2</v>
+        <v>52.4</v>
       </c>
       <c r="T143" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U143" t="n">
-        <v>75.59999999999999</v>
+        <v>25.3</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -40125,27 +40125,27 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL143" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 9.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
@@ -40155,57 +40155,57 @@
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>39.62</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>84.98</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>96.7242</t>
+          <t>99.866</t>
         </is>
       </c>
       <c r="AR143" t="inlineStr">
         <is>
-          <t>0.3999</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>0.3091</t>
+          <t>0.3221</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>70.75</t>
+          <t>72.38</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>37.66</t>
+          <t>44.08</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -40215,52 +40215,52 @@
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>0.1858</t>
+          <t>0.1105</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>86.79</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD143" t="inlineStr">
         <is>
-          <t>0.3513</t>
+          <t>0.4022</t>
         </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
-          <t>0.1183</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="BG143" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH143" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI143" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ143" t="inlineStr"/>
@@ -40551,27 +40551,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>671083</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Buddy Kennedy</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-14T23:10:00Z</t>
+          <t>2026-08-15T02:15:00Z</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -40581,22 +40581,22 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>650633</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L145" t="n">
@@ -40618,22 +40618,22 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>30.2</v>
+        <v>9.6</v>
       </c>
       <c r="Q145" t="n">
-        <v>39.4</v>
+        <v>59.3</v>
       </c>
       <c r="R145" t="n">
-        <v>41.1</v>
+        <v>50.3</v>
       </c>
       <c r="S145" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T145" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U145" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -40685,27 +40685,27 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 0/10, 0 HR</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.4% barrel, 21.3 HR allowed</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -40715,112 +40715,112 @@
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>38.92</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>83.98</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>99.413</t>
+          <t>96.1775</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>0.3652</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>0.1433</t>
+          <t>0.0465</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>0.2822</t>
+          <t>0.1775</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>71.21</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>0.1072</t>
+          <t>0.0389</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>43.94</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>0.4102</t>
+          <t>0.4772</t>
         </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1945</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH145" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>60</t>
         </is>
       </c>
       <c r="BI145" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ145" t="inlineStr"/>
@@ -40831,47 +40831,47 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>671083</t>
+          <t>805999</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Buddy Kennedy</t>
+          <t>A.J. Ewing</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-15T02:15:00Z</t>
+          <t>2026-08-14T23:10:00Z</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -40880,7 +40880,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
@@ -40894,26 +40894,26 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>9.6</v>
+        <v>32.1</v>
       </c>
       <c r="Q146" t="n">
-        <v>59.3</v>
+        <v>19.8</v>
       </c>
       <c r="R146" t="n">
-        <v>50.3</v>
+        <v>47.8</v>
       </c>
       <c r="S146" t="n">
-        <v>64.3</v>
+        <v>93.2</v>
       </c>
       <c r="T146" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U146" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
@@ -40948,7 +40948,7 @@
       <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr"/>
@@ -40965,27 +40965,27 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/10, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.4% barrel, 21.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.1% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
@@ -40995,112 +40995,112 @@
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>83.98</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>96.1775</t>
+          <t>100.4707</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.398</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>0.0465</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>0.1775</t>
+          <t>0.322</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>71.21</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>0.0389</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>43.94</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.25</t>
         </is>
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>0.4772</t>
+          <t>0.3416</t>
         </is>
       </c>
       <c r="BE146" t="inlineStr">
         <is>
-          <t>0.1945</t>
+          <t>0.0983</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH146" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI146" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ146" t="inlineStr"/>
@@ -41111,22 +41111,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>805999</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>A.J. Ewing</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -41141,22 +41141,22 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>650633</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -41174,26 +41174,26 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P147" t="n">
-        <v>32.1</v>
+        <v>30.2</v>
       </c>
       <c r="Q147" t="n">
-        <v>19.8</v>
+        <v>39.4</v>
       </c>
       <c r="R147" t="n">
-        <v>47.8</v>
+        <v>40.1</v>
       </c>
       <c r="S147" t="n">
-        <v>93.2</v>
+        <v>52.4</v>
       </c>
       <c r="T147" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U147" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -41228,7 +41228,7 @@
       <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr"/>
@@ -41245,27 +41245,27 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.1% barrel, 1.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.4% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
@@ -41275,112 +41275,112 @@
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>38.92</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>100.4707</t>
+          <t>99.413</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>0.3652</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.1433</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>0.2822</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>32.99</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1072</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>89.25</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="BD147" t="inlineStr">
         <is>
-          <t>0.3416</t>
+          <t>0.4102</t>
         </is>
       </c>
       <c r="BE147" t="inlineStr">
         <is>
-          <t>0.0983</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>27.61</t>
         </is>
       </c>
       <c r="BG147" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH147" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI147" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ147" t="inlineStr"/>
@@ -42511,52 +42511,52 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>545121</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Luis Rengifo</t>
+          <t>Ildemaro Vargas</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-14T23:10:00Z</t>
+          <t>2026-08-14T23:15:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -42574,50 +42574,42 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q152" t="n">
-        <v>52.9</v>
+        <v>21</v>
       </c>
       <c r="R152" t="n">
-        <v>41.1</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="S152" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T152" t="n">
         <v>75</v>
       </c>
       <c r="U152" t="n">
-        <v>46.5</v>
+        <v>10.1</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="W152" t="inlineStr"/>
+      <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -42625,7 +42617,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC152" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -42645,27 +42641,27 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.0% barrel, 8.9 HR allowed</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
@@ -42675,112 +42671,112 @@
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>34.03</t>
+          <t>35.97</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>97.8804</t>
+          <t>98.6209</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.3575</t>
+          <t>0.3837</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0.0989</t>
+          <t>0.1063</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.3076</t>
+          <t>0.3066</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>70.83</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>14.79</t>
+          <t>14.54</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>0.0809</t>
+          <t>0.1284</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>87.41</t>
         </is>
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>0.4022</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="BE152" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1101</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH152" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr"/>
@@ -42791,56 +42787,56 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>545121</t>
+          <t>650859</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ildemaro Vargas</t>
+          <t>Luis Rengifo</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-14T23:15:00Z</t>
+          <t>2026-08-14T23:10:00Z</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
@@ -42854,54 +42850,58 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P153" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Q153" t="n">
-        <v>21</v>
+        <v>52.9</v>
       </c>
       <c r="R153" t="n">
-        <v>72.40000000000001</v>
+        <v>40.1</v>
       </c>
       <c r="S153" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T153" t="n">
         <v>75</v>
       </c>
       <c r="U153" t="n">
-        <v>10.1</v>
+        <v>46.5</v>
       </c>
       <c r="V153" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W153" t="inlineStr"/>
-      <c r="X153" t="inlineStr"/>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y153" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -42921,27 +42921,27 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.0% barrel, 8.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.6% barrel, 22.3 HR allowed</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
@@ -42951,112 +42951,112 @@
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>34.03</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>98.6209</t>
+          <t>97.8804</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>0.3837</t>
+          <t>0.3575</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>0.1063</t>
+          <t>0.0989</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>0.3066</t>
+          <t>0.3076</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>70.83</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>14.79</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>0.1284</t>
+          <t>0.0809</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>87.41</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.4022</t>
         </is>
       </c>
       <c r="BE153" t="inlineStr">
         <is>
-          <t>0.1101</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="BG153" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH153" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI153" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ153" t="inlineStr"/>
@@ -43092,7 +43092,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -43116,7 +43116,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>41</v>
       </c>
       <c r="R154" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S154" t="n">
         <v>93.2</v>
@@ -43331,7 +43331,7 @@
       </c>
       <c r="BH154" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI154" t="inlineStr">
@@ -43372,7 +43372,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -43928,7 +43928,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -46136,7 +46136,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -46416,7 +46416,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -46440,7 +46440,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
@@ -46464,7 +46464,7 @@
         <v>41</v>
       </c>
       <c r="R166" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S166" t="n">
         <v>64.3</v>
@@ -46655,7 +46655,7 @@
       </c>
       <c r="BH166" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI166" t="inlineStr">
@@ -47256,7 +47256,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -47536,7 +47536,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -48628,7 +48628,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -48908,7 +48908,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -48932,7 +48932,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -48956,7 +48956,7 @@
         <v>39.4</v>
       </c>
       <c r="R175" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S175" t="n">
         <v>44.8</v>
@@ -49147,7 +49147,7 @@
       </c>
       <c r="BH175" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI175" t="inlineStr">
@@ -49472,7 +49472,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -49980,7 +49980,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -51706,7 +51706,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -51986,7 +51986,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -52266,7 +52266,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -52546,7 +52546,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -53386,7 +53386,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -54786,7 +54786,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -55346,7 +55346,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -55874,7 +55874,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
